--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486550_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486550_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. POLYNICE</t>
+          <t>K. WEBSTER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5071</v>
+        <v>2.0364</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0413</v>
+        <v>1.2378</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5341</v>
+        <v>0.7987</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.9676</v>
+        <v>1.0376</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8544</v>
+        <v>-0.8303</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.1132</v>
+        <v>1.8679</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2996</v>
+        <v>2.1637</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3706</v>
+        <v>-0.976</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6702</v>
+        <v>3.1397</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.2672</v>
+        <v>-1.1261</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4838</v>
+        <v>0.1457</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.7834</v>
+        <v>-1.2718</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3872</v>
+        <v>-0.2839</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6117</v>
+        <v>-0.0336</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2245</v>
+        <v>-0.2503</v>
       </c>
       <c r="V2" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. WEBSTER</t>
+          <t>S. SVEJCAR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1181</v>
+        <v>1.3853</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4735</v>
+        <v>0.2184</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6446</v>
+        <v>1.1669</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0376</v>
+        <v>-1.9863</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8303</v>
+        <v>-0.5687</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8679</v>
+        <v>-1.4176</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1637</v>
+        <v>-1.1941</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.976</v>
+        <v>-0.8149</v>
       </c>
       <c r="L3" t="n">
-        <v>3.1397</v>
+        <v>-0.3793</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1261</v>
+        <v>-0.7922</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1457</v>
+        <v>0.2461</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2718</v>
+        <v>-1.0383</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1751</v>
+        <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2023</v>
+        <v>0.1319</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.0649</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4044</v>
+        <v>0.1968</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1952</v>
+        <v>1.4997</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1952</v>
+        <v>1.695</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. GARUBA ALARI</t>
+          <t>C. POLYNICE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5823</v>
+        <v>1.1037</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07820000000000001</v>
+        <v>1.5762</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5041</v>
+        <v>-0.4725</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1403</v>
+        <v>-1.9676</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2415</v>
+        <v>-0.8544</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.3818</v>
+        <v>-1.1132</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9499</v>
+        <v>0.2996</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8463</v>
+        <v>-0.3706</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8964</v>
+        <v>0.6702</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0902</v>
+        <v>-2.2672</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3951</v>
+        <v>-0.4838</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4854</v>
+        <v>-1.7834</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2175</v>
+        <v>1.9576</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1799</v>
+        <v>-0.0162</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1093</v>
+        <v>0.1466</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2892</v>
+        <v>-0.1628</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7602</v>
+        <v>1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7602</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. SVEJCAR</t>
+          <t>A. GARUBA ALARI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5787</v>
+        <v>0.4718</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4341</v>
+        <v>0.0602</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0128</v>
+        <v>0.4116</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.9863</v>
+        <v>-0.1403</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5687</v>
+        <v>2.2415</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4176</v>
+        <v>-2.3818</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.1941</v>
+        <v>0.9499</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8149</v>
+        <v>1.8463</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3793</v>
+        <v>-0.8964</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7922</v>
+        <v>-1.0902</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2461</v>
+        <v>0.3951</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0383</v>
+        <v>-1.4854</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7401</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2175</v>
+        <v>-1.5225</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6748</v>
+        <v>0.0694</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7174</v>
+        <v>-0.1274</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0427</v>
+        <v>0.1968</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4997</v>
+        <v>0.7602</v>
       </c>
       <c r="W5" t="n">
-        <v>1.695</v>
+        <v>0.7602</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2841</v>
+        <v>0.3034</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0862</v>
+        <v>0.198</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1979</v>
+        <v>0.1054</v>
       </c>
       <c r="G6" t="n">
         <v>1.3888</v>
@@ -922,13 +922,13 @@
         <v>0.2175</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2347</v>
+        <v>-0.2154</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1662</v>
+        <v>-0.2587</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06610000000000001</v>
+        <v>-0.3797</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.4496</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7368</v>
+        <v>-0.8293</v>
       </c>
       <c r="G7" t="n">
         <v>-1.5558</v>
@@ -1000,13 +1000,13 @@
         <v>2.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5344</v>
+        <v>0.0886</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3942</v>
+        <v>0.0409</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1402</v>
+        <v>0.0478</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4127</v>
+        <v>-0.4974</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6349</v>
+        <v>-0.4113</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2222</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7311</v>
@@ -1078,13 +1078,13 @@
         <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1009</v>
+        <v>0.0162</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6609</v>
+        <v>-0.4374</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7619</v>
+        <v>0.4536</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9831</v>
+        <v>-3.38</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1433</v>
+        <v>-0.192</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.1264</v>
+        <v>-3.188</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5893</v>
@@ -1156,13 +1156,13 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4985</v>
+        <v>0.1015</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0156</v>
+        <v>-0.3196</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4828</v>
+        <v>0.4212</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9347</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.239</v>
+        <v>-5.8807</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1207</v>
+        <v>-2.009</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.1183</v>
+        <v>-3.8717</v>
       </c>
       <c r="G10" t="n">
         <v>-4.2187</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1731</v>
+        <v>-0.8147</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8784</v>
+        <v>-0.7667</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2947</v>
+        <v>-0.0481</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4997</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.6058</v>
+        <v>-6.2397</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.0422</v>
+        <v>-5.7069</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5636</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0347</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.5074</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0154</v>
+        <v>-0.6801</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1419</v>
+        <v>0.1727</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.1042</v>
+        <v>-11.0769</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.6065</v>
+        <v>-4.579000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.497599999999999</v>
+        <v>-6.4977</v>
       </c>
       <c r="G12" t="n">
         <v>-10.7974</v>
@@ -1381,7 +1381,7 @@
         <v>-19.4236</v>
       </c>
       <c r="P12" t="n">
-        <v>-8.881784197001252e-16</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.0503</v>
@@ -1390,13 +1390,13 @@
         <v>13.0504</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.4575</v>
+        <v>-1.43</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.2263</v>
+        <v>-2.1989</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7689</v>
+        <v>0.769</v>
       </c>
       <c r="V12" t="n">
         <v>1.1507</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>A. KUNKEL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2429</v>
+        <v>4.4684</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3808</v>
+        <v>2.0778</v>
       </c>
       <c r="F13" t="n">
-        <v>4.6237</v>
+        <v>2.3906</v>
       </c>
       <c r="G13" t="n">
-        <v>3.1349</v>
+        <v>6.2607</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8273</v>
+        <v>0.7328</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3077</v>
+        <v>5.5278</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3676</v>
+        <v>5.7899</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0616</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>0.306</v>
+        <v>4.8226</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7673</v>
+        <v>0.4708</v>
       </c>
       <c r="N13" t="n">
         <v>-0.2344</v>
       </c>
       <c r="O13" t="n">
-        <v>2.0017</v>
+        <v>0.7052</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.435</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R13" t="n">
         <v>1.7401</v>
       </c>
       <c r="S13" t="n">
-        <v>1.543</v>
+        <v>-0.0745</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4266</v>
+        <v>-0.4494</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1164</v>
+        <v>0.3749</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9643</v>
+        <v>4.2687</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7338</v>
+        <v>4.6221</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7696</v>
+        <v>-0.3533</v>
       </c>
       <c r="G14" t="n">
         <v>4.4427</v>
@@ -1546,13 +1546,13 @@
         <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4145</v>
+        <v>0.7189</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1526</v>
+        <v>0.0409</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2618</v>
+        <v>0.678</v>
       </c>
       <c r="V14" t="n">
         <v>1.4997</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. KUNKEL</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6027</v>
+        <v>3.7111</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8543</v>
+        <v>-0.6044</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7484</v>
+        <v>4.3155</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2607</v>
+        <v>3.1349</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7328</v>
+        <v>0.8273</v>
       </c>
       <c r="I15" t="n">
-        <v>5.5278</v>
+        <v>2.3077</v>
       </c>
       <c r="J15" t="n">
-        <v>5.7899</v>
+        <v>1.3676</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9671999999999999</v>
+        <v>1.0616</v>
       </c>
       <c r="L15" t="n">
-        <v>4.8226</v>
+        <v>0.306</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4708</v>
+        <v>1.7673</v>
       </c>
       <c r="N15" t="n">
         <v>-0.2344</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7052</v>
+        <v>2.0017</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5225</v>
+        <v>-0.435</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R15" t="n">
         <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9402</v>
+        <v>1.0112</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.2031</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2673</v>
+        <v>0.8081</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. WINTERING</t>
+          <t>J. VRANKIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.701</v>
+        <v>2.7664</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4588</v>
+        <v>-0.3338</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2421</v>
+        <v>3.1003</v>
       </c>
       <c r="G16" t="n">
-        <v>2.067</v>
+        <v>3.0885</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.4329</v>
+        <v>0.8031</v>
       </c>
       <c r="I16" t="n">
-        <v>4.4998</v>
+        <v>2.2854</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6607</v>
+        <v>2.2041</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.0495</v>
+        <v>0.922</v>
       </c>
       <c r="L16" t="n">
-        <v>3.7102</v>
+        <v>1.2822</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4063</v>
+        <v>0.8844</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3834</v>
+        <v>-0.1188</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7897</v>
+        <v>1.0032</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6525</v>
+        <v>-0.435</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
         <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7417</v>
+        <v>0.113</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8857</v>
+        <v>-0.3629</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.144</v>
+        <v>0.4759</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>A. WINTERING</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3814</v>
+        <v>2.2885</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4299</v>
+        <v>0.6765</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8113</v>
+        <v>1.612</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7082000000000001</v>
+        <v>2.067</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.8434</v>
+        <v>-2.4329</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5516</v>
+        <v>4.4998</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3218</v>
+        <v>1.6607</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.7581</v>
+        <v>-2.0495</v>
       </c>
       <c r="L17" t="n">
-        <v>3.0799</v>
+        <v>3.7102</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3863</v>
+        <v>0.4063</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0854</v>
+        <v>-0.3834</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4717</v>
+        <v>0.7897</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5204</v>
+        <v>0.3293</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9469</v>
+        <v>0.1034</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4674</v>
+        <v>0.2259</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3698</v>
+        <v>-0.7602</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. VRANKIC</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2937</v>
+        <v>2.28</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7809</v>
+        <v>-0.0946</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0746</v>
+        <v>2.3746</v>
       </c>
       <c r="G18" t="n">
-        <v>3.0885</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8031</v>
+        <v>-2.8434</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2854</v>
+        <v>3.5516</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2041</v>
+        <v>0.3218</v>
       </c>
       <c r="K18" t="n">
-        <v>0.922</v>
+        <v>-2.7581</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2822</v>
+        <v>3.0799</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8844</v>
+        <v>0.3863</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1188</v>
+        <v>-0.0854</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0032</v>
+        <v>0.4717</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3598</v>
+        <v>0.4191</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8099</v>
+        <v>-0.6117</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4501</v>
+        <v>1.0307</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8188</v>
+        <v>1.5947</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5606</v>
+        <v>2.0076</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7418</v>
+        <v>-0.4129</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6862</v>
@@ -1936,13 +1936,13 @@
         <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2775</v>
+        <v>0.4984</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3869</v>
+        <v>0.0601</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1095</v>
+        <v>0.4383</v>
       </c>
       <c r="V19" t="n">
         <v>1.13</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>M. RODRIGUEZ BARRIENTOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1952</v>
+        <v>-0.1678</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3673</v>
+        <v>-0.8628</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1721</v>
+        <v>0.695</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2762</v>
+        <v>-0.3874</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.916</v>
+        <v>0.5991</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3602</v>
+        <v>-0.9865</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0784</v>
+        <v>-0.6321</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4171</v>
+        <v>0.0365</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3387</v>
+        <v>-0.6686</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1978</v>
+        <v>0.2446</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4989</v>
+        <v>0.5626</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6989</v>
+        <v>-0.318</v>
       </c>
       <c r="P20" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>1.6014</v>
+        <v>-0.0201</v>
       </c>
       <c r="T20" t="n">
-        <v>1.4456</v>
+        <v>-0.2307</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1557</v>
+        <v>0.2106</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ BARRIENTOS</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.521</v>
+        <v>-0.4496</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9745</v>
+        <v>0.6967</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4535</v>
+        <v>-1.1464</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3874</v>
+        <v>-2.2762</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5991</v>
+        <v>-1.916</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9865</v>
+        <v>-0.3602</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6321</v>
+        <v>-0.0784</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0365</v>
+        <v>-1.4171</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6686</v>
+        <v>1.3387</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2446</v>
+        <v>-2.1978</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5626</v>
+        <v>-0.4989</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.318</v>
+        <v>-1.6989</v>
       </c>
       <c r="P21" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3734</v>
+        <v>0.9566</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3425</v>
+        <v>0.7751</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0309</v>
+        <v>0.1815</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. LEVY</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4481</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1949</v>
+        <v>1.3998</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.643</v>
+        <v>-1.9305</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6055</v>
+        <v>-0.7328</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0432</v>
+        <v>-0.654</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6487</v>
+        <v>-0.0789</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5564</v>
+        <v>1.4515</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4417</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1147</v>
+        <v>2.087</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1619</v>
+        <v>-2.1843</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3985</v>
+        <v>-0.0184</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.7635</v>
+        <v>-2.1659</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.87</v>
+        <v>0.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0274</v>
+        <v>0.4621</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.274</v>
+        <v>-0.0517</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3014</v>
+        <v>0.5137</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>G. LEVY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4722</v>
+        <v>-1.5098</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0645</v>
+        <v>0.1949</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5368</v>
+        <v>-1.7047</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7328</v>
+        <v>-0.6055</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.654</v>
+        <v>1.0432</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0789</v>
+        <v>-1.6487</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4515</v>
+        <v>1.5564</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6356000000000001</v>
+        <v>1.4417</v>
       </c>
       <c r="L23" t="n">
-        <v>2.087</v>
+        <v>0.1147</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1843</v>
+        <v>-2.1619</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0184</v>
+        <v>-0.3985</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.1659</v>
+        <v>-1.7635</v>
       </c>
       <c r="P23" t="n">
-        <v>0.87</v>
+        <v>-0.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R23" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4795</v>
+        <v>-0.0342</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3869</v>
+        <v>-0.274</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0925</v>
+        <v>0.2397</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6543</v>
+        <v>-4.3806</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1703</v>
+        <v>-3.2821</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4839</v>
+        <v>-1.0986</v>
       </c>
       <c r="G24" t="n">
         <v>-4.2162</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0394</v>
+        <v>0.313</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1406</v>
+        <v>0.0288</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1012</v>
+        <v>0.2842</v>
       </c>
       <c r="V24" t="n">
         <v>-1.13</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>12.1044</v>
+        <v>14.3393</v>
       </c>
       <c r="E25" t="n">
-        <v>6.497800000000001</v>
+        <v>6.497700000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>5.606400000000001</v>
+        <v>7.841599999999997</v>
       </c>
       <c r="G25" t="n">
         <v>10.7977</v>
@@ -2380,7 +2380,7 @@
         <v>17.2971</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.1266</v>
+        <v>-2.126600000000001</v>
       </c>
       <c r="L25" t="n">
         <v>19.4235</v>
@@ -2392,7 +2392,7 @@
         <v>-0.6862999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-5.813400000000001</v>
+        <v>-5.8134</v>
       </c>
       <c r="P25" t="n">
         <v>-0.000100000000000211</v>
@@ -2404,13 +2404,13 @@
         <v>13.0504</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4574</v>
+        <v>4.6928</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7689000000000001</v>
+        <v>-0.7689999999999998</v>
       </c>
       <c r="U25" t="n">
-        <v>3.226400000000001</v>
+        <v>5.4615</v>
       </c>
       <c r="V25" t="n">
         <v>-1.1507</v>
